--- a/tools/predict_model_specs.xlsx
+++ b/tools/predict_model_specs.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">na</t>
   </si>
   <si>
-    <t xml:space="preserve">N</t>
+    <t xml:space="preserve">Y</t>
   </si>
   <si>
     <t xml:space="preserve">1997_2009</t>
